--- a/data/GlobalVariable.xlsx
+++ b/data/GlobalVariable.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,16 @@
           <t>uint32</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>uint32</t>
@@ -490,116 +500,115 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>designer</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>constants_name</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5"/>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>非正常下线时间</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Abnormal_logout</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1200</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>非正常下线时间</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Abnormal_logout</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1200</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
         <v>16</v>
       </c>
     </row>

--- a/data/GlobalVariable.xlsx
+++ b/data/GlobalVariable.xlsx
@@ -434,27 +434,27 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>touint32</t>
+          <t>to_uint32</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>toint32</t>
+          <t>to_int32</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>tostring</t>
+          <t>to_string</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>tofloat</t>
+          <t>to_float</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>todouble</t>
+          <t>to_double</t>
         </is>
       </c>
     </row>
@@ -517,8 +517,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
         <v>1</v>
